--- a/test-data/xlsx/import_preview_invalid.xlsx
+++ b/test-data/xlsx/import_preview_invalid.xlsx
@@ -20,12 +20,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
-  <si>
-    <t xml:space="preserve">jobTitle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">companyName</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+  <si>
+    <t xml:space="preserve">Job Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employment Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mountain View CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seattle</t>
   </si>
 </sst>
 </file>
@@ -227,11 +260,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.09"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -240,6 +275,48 @@
       </c>
       <c r="B1" s="0" t="s">
         <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
